--- a/www/flightdata/xlsx/eoss-363.xlsx
+++ b/www/flightdata/xlsx/eoss-363.xlsx
@@ -3750,7 +3750,7 @@
         <v>32334.71</v>
       </c>
       <c r="I2">
-        <v>745</v>
+        <v>488</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
